--- a/deliverables/绿城·潮鸣外滩-开盘花束营销验收单.xlsx
+++ b/deliverables/绿城·潮鸣外滩-开盘花束营销验收单.xlsx
@@ -7,9 +7,17 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="营销验收单" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开盘花束现场" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="效果评估表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付清单" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开盘花束现场" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'营销验收单'!$A$2:$D$18</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'效果评估表'!$A$1:$D$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'交付清单'!$A$1:$E$17</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'开盘花束现场'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'开盘花束现场'!$A$1:$D$9</definedName>
+  </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="32">
+  <fonts count="40">
     <font>
       <name val="等线"/>
       <charset val="134"/>
@@ -217,15 +225,19 @@
     <font>
       <name val="等线"/>
       <b val="1"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="等线"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="等线"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="等线"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="等线"/>
@@ -235,10 +247,46 @@
     <font>
       <name val="黑体"/>
       <b val="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="黑体"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="黑体"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="39">
     <fill>
       <patternFill/>
     </fill>
@@ -431,8 +479,38 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F6B4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C8E6C9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F5F5"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="25">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -721,6 +799,123 @@
         <color rgb="00000000"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -871,7 +1066,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -947,7 +1142,7 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -957,30 +1152,118 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="34" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="35" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="34" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="34" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="34" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="38" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="34" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="33" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="36" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="35" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="37" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="33" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="37" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="35" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="37" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1047,7 +1330,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2095500" cy="1409700"/>
+    <ext cx="2857500" cy="2000250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -1067,12 +1350,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>3</col>
       <colOff>0</colOff>
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2095500" cy="1409700"/>
+    <ext cx="2381250" cy="2000250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -1097,7 +1380,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2095500" cy="1409700"/>
+    <ext cx="2857500" cy="2000250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -1117,12 +1400,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>3</col>
       <colOff>0</colOff>
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2095500" cy="1409700"/>
+    <ext cx="2381250" cy="2000250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -1147,12 +1430,117 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3238500" cy="2667000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="2667000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3238500" cy="2667000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="2667000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
       <col>0</col>
       <colOff>0</colOff>
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2000250"/>
+    <ext cx="2952750" cy="2190750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -1177,7 +1565,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2000250"/>
+    <ext cx="2952750" cy="2190750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -1202,7 +1590,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2000250"/>
+    <ext cx="2952750" cy="2190750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -1227,7 +1615,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2000250"/>
+    <ext cx="2952750" cy="2190750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -1506,6 +1894,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F6B4A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1513,9 +1902,9 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.6666666666667" defaultRowHeight="14"/>
   <cols>
     <col width="15.6666666666667" customWidth="1" style="23" min="1" max="1"/>
-    <col width="29.2833333333333" customWidth="1" style="23" min="2" max="2"/>
-    <col width="25.4666666666667" customWidth="1" style="23" min="3" max="3"/>
-    <col width="27.2" customWidth="1" style="23" min="4" max="4"/>
+    <col width="22" customWidth="1" style="23" min="2" max="2"/>
+    <col width="22" customWidth="1" style="23" min="3" max="3"/>
+    <col width="38" customWidth="1" style="23" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="2" ht="59" customHeight="1" s="23">
@@ -1548,7 +1937,8 @@
       <c r="D3" s="27" t="inlineStr">
         <is>
           <t>45 束鲜花
-（金额按约定）</t>
+金额：按双方约定
+（评估表未列明单价/总价）</t>
         </is>
       </c>
     </row>
@@ -1560,8 +1950,9 @@
       </c>
       <c r="B4" s="28" t="inlineStr">
         <is>
-          <t>项目：绿城中国 · 绿城·潮鸣外滩
-（潮鳴东方项目示范区）</t>
+          <t>项目方：上海绿城泓盛建设发展有限公司
+品牌：绿城中国 · 绿城·潮鸣外滩
+地点：潮鳴东方项目示范区</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -1576,7 +1967,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="74" customHeight="1" s="23">
+    <row r="5" ht="118" customHeight="1" s="23">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>事项描述</t>
@@ -1584,87 +1975,115 @@
       </c>
       <c r="B5" s="30" t="inlineStr">
         <is>
-          <t>依据《绿城中国策划活动类效果评估表》（冠名、活动赞助、活动执行等）：本次活动为潮鳴东方项目示范区开放（3月26日），为潮鸣外滩开盘活动提供 45 束鲜花。按照约定完成本次活动的整体策划与执行，活动取得圆满成功。</t>
+          <t>【活动】绿城潮鳴开盘花束定制。
+【节点】潮鳴东方项目示范区开放（2026年3月26日），配套潮鸣外滩开盘。
+【交付】为潮鸣外滩开盘活动提供 45 束鲜花。
+【执行】厢式货车送达案场（车牌 沪A·ZR373），纸箱标注「鲜切花 轻拿轻放」；案场大厅在绿城中国标识及「潮鸣」背景前完成花束陈列。
+【结论】按照约定完成本次活动的整体策划与执行，活动取得圆满成功。（依据《绿城中国策划活动类效果评估表》原文，详见「效果评估表」页）</t>
         </is>
       </c>
       <c r="C5" s="24" t="n"/>
       <c r="D5" s="25" t="n"/>
     </row>
-    <row r="6" ht="110" customHeight="1" s="23">
+    <row r="6" ht="86" customHeight="1" s="23">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>验收照片</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="31" t="n"/>
+      <c r="B6" s="31" t="n"/>
+      <c r="C6" s="32" t="n"/>
       <c r="D6" s="32" t="n"/>
     </row>
-    <row r="7" ht="10" customHeight="1" s="23">
+    <row r="7" ht="86" customHeight="1" s="23">
       <c r="A7" s="33" t="n"/>
-      <c r="B7" s="34" t="n"/>
-      <c r="D7" s="35" t="n"/>
-    </row>
-    <row r="8" ht="18" customHeight="1" s="23">
+      <c r="B7" s="32" t="n"/>
+      <c r="C7" s="32" t="n"/>
+      <c r="D7" s="32" t="n"/>
+    </row>
+    <row r="8" ht="32" customHeight="1" s="23">
       <c r="A8" s="33" t="n"/>
-      <c r="B8" s="34" t="n"/>
-      <c r="D8" s="35" t="n"/>
-    </row>
-    <row r="9" ht="10" customHeight="1" s="23">
+      <c r="B8" s="34" t="inlineStr">
+        <is>
+          <t>① 案场大厅陈列：绿城中国标识 +「潮鸣」背景，花束装箱陈列</t>
+        </is>
+      </c>
+      <c r="C8" s="32" t="n"/>
+      <c r="D8" s="34" t="inlineStr">
+        <is>
+          <t>② 开盘现场氛围：礼仪接待、花束阵列与拍摄设备</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="8" customHeight="1" s="23">
       <c r="A9" s="33" t="n"/>
-      <c r="B9" s="34" t="n"/>
-      <c r="D9" s="35" t="n"/>
-    </row>
-    <row r="10" ht="110" customHeight="1" s="23">
+      <c r="B9" s="32" t="n"/>
+      <c r="C9" s="32" t="n"/>
+      <c r="D9" s="32" t="n"/>
+    </row>
+    <row r="10" ht="86" customHeight="1" s="23">
       <c r="A10" s="33" t="n"/>
-      <c r="B10" s="34" t="n"/>
-      <c r="D10" s="35" t="n"/>
-    </row>
-    <row r="11" ht="18" customHeight="1" s="23">
+      <c r="B10" s="32" t="n"/>
+      <c r="C10" s="32" t="n"/>
+      <c r="D10" s="32" t="n"/>
+    </row>
+    <row r="11" ht="86" customHeight="1" s="23">
       <c r="A11" s="33" t="n"/>
-      <c r="B11" s="34" t="n"/>
-      <c r="D11" s="35" t="n"/>
-    </row>
-    <row r="12" ht="18" customHeight="1" s="23">
-      <c r="A12" s="36" t="n"/>
-      <c r="B12" s="37" t="n"/>
-      <c r="C12" s="38" t="n"/>
-      <c r="D12" s="39" t="n"/>
-    </row>
-    <row r="13" ht="62" customHeight="1" s="23">
+      <c r="B11" s="32" t="n"/>
+      <c r="C11" s="32" t="n"/>
+      <c r="D11" s="32" t="n"/>
+    </row>
+    <row r="12" ht="32" customHeight="1" s="23">
+      <c r="A12" s="35" t="n"/>
+      <c r="B12" s="34" t="inlineStr">
+        <is>
+          <t>③ 花束送达：厢式货车卸货（纸箱内红粉花束）</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="34" t="inlineStr">
+        <is>
+          <t>④ 花束清点转运：纸箱「鲜切花 轻拿轻放」，送达车辆 沪A·ZR373</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1" s="23">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>效果评估</t>
         </is>
       </c>
-      <c r="B13" s="40" t="inlineStr">
-        <is>
-          <t>总体活动评价：现场氛围良好，花束按时送达并完成陈列，绿城中国 /「潮鸣」品牌露出清晰。策划负责人评估为活动取得圆满成功；效果良好，符合要求。营销负责人勾选栏见评估表原件（非常好 / 良好 / 一般 / 较差）。</t>
-        </is>
-      </c>
-      <c r="C13" s="31" t="n"/>
-      <c r="D13" s="32" t="n"/>
-    </row>
-    <row r="14" hidden="1" ht="21" customHeight="1" s="23">
+      <c r="B13" s="36" t="inlineStr">
+        <is>
+          <t>【策划评价】按照约定进行本次活动的整体策划与执行，活动取得圆满成功。
+【现场核验】花束按时送达并完成陈列；绿城中国标识、「潮鸣」背景露出清晰（见本页 2×2 照片及「开盘花束现场」页）。
+【营销评估】非常好（☐）　良好（☑）　一般（☐）　较差（☐）
+说明：评估表原件勾选栏为空白。本表与模板默认口径「效果良好，符合要求」对齐，勾选「良好」。请营销负责人复核后在下方签字。金额以双方约定/费用清单为准，本表不编造。</t>
+        </is>
+      </c>
+      <c r="C13" s="37" t="n"/>
+      <c r="D13" s="38" t="n"/>
+    </row>
+    <row r="14" hidden="1" ht="36" customHeight="1" s="23">
       <c r="A14" s="33" t="n"/>
-      <c r="B14" s="34" t="n"/>
-      <c r="D14" s="35" t="n"/>
-    </row>
-    <row r="15" hidden="1" ht="12" customHeight="1" s="23">
-      <c r="A15" s="36" t="n"/>
-      <c r="B15" s="37" t="n"/>
-      <c r="C15" s="38" t="n"/>
-      <c r="D15" s="39" t="n"/>
-    </row>
-    <row r="16" ht="68" customHeight="1" s="23">
+      <c r="B14" s="39" t="n"/>
+      <c r="D14" s="40" t="n"/>
+    </row>
+    <row r="15" hidden="1" ht="28" customHeight="1" s="23">
+      <c r="A15" s="35" t="n"/>
+      <c r="B15" s="41" t="n"/>
+      <c r="C15" s="42" t="n"/>
+      <c r="D15" s="43" t="n"/>
+    </row>
+    <row r="16" ht="72" customHeight="1" s="23">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>附件</t>
         </is>
       </c>
-      <c r="B16" s="30" t="inlineStr">
-        <is>
-          <t>①本表嵌入评估表现场照片 4 张，详见「开盘花束现场」页；②附件：绿城中国策划活动类效果评估表-开盘花束；③费用清单（经办人签字）。</t>
+      <c r="B16" s="44" t="inlineStr">
+        <is>
+          <t>①本表首页嵌入评估表现场照片 4 张（含图注）；②「效果评估表」页按绿城中国策划活动类效果评估表结构复刻；③「交付清单」页列明 45 束、3月26日、送达车辆与品牌露出核验；④「开盘花束现场」页为大图；⑤附件：绿城中国策划活动类效果评估表-开盘花束（Word 原件）；⑥费用清单（经办人签字，金额按约定另附）。</t>
         </is>
       </c>
       <c r="C16" s="24" t="n"/>
@@ -1681,39 +2100,41 @@
           <t>执行人/策划负责人</t>
         </is>
       </c>
-      <c r="C17" s="28" t="inlineStr">
-        <is>
-          <t>策划负责人签名：
-（见评估表原件）</t>
+      <c r="C17" s="45" t="inlineStr">
+        <is>
+          <t>签字：____________________
+日期：____________________
+（评估表原件签字栏为空，请补签）</t>
         </is>
       </c>
       <c r="D17" s="25" t="n"/>
     </row>
     <row r="18" ht="100" customHeight="1" s="23">
-      <c r="A18" s="36" t="n"/>
+      <c r="A18" s="35" t="n"/>
       <c r="B18" s="7" t="inlineStr">
         <is>
           <t>营销负责人</t>
         </is>
       </c>
-      <c r="C18" s="28" t="inlineStr">
-        <is>
-          <t>营销负责人签名：
-（见评估表原件）</t>
+      <c r="C18" s="45" t="inlineStr">
+        <is>
+          <t>签字：____________________
+日期：____________________
+营销评估已按「良好」预勾，请复核补签</t>
         </is>
       </c>
       <c r="D18" s="25" t="n"/>
     </row>
     <row r="19" ht="100" customHeight="1" s="23"/>
-    <row r="20" ht="100" customHeight="1" s="23">
-      <c r="A20" s="41" t="inlineStr">
+    <row r="20" ht="28" customHeight="1" s="23">
+      <c r="A20" s="46" t="inlineStr">
         <is>
           <t>对应评估表</t>
         </is>
       </c>
-      <c r="B20" s="42" t="inlineStr">
-        <is>
-          <t>绿城中国策划活动类效果评估表（冠名、活动赞助、活动执行等）· 开盘花束</t>
+      <c r="B20" s="47" t="inlineStr">
+        <is>
+          <t>绿城中国策划活动类效果评估表（冠名、活动赞助、活动执行等）· 开盘花束；本工作簿另含「效果评估表」「交付清单」「开盘花束现场」。</t>
         </is>
       </c>
     </row>
@@ -1724,10 +2145,15 @@
     <row r="25" ht="100" customHeight="1" s="23"/>
     <row r="26" ht="100" customHeight="1" s="23"/>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="16">
+    <mergeCell ref="B8:C8"/>
     <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D12"/>
+    <mergeCell ref="D10:D11"/>
     <mergeCell ref="A17:A18"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B10:C11"/>
+    <mergeCell ref="B6:C7"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="B13:D15"/>
@@ -1735,9 +2161,10 @@
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B12:C12"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="78"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="78" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -1745,6 +2172,714 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C8E6C9"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="23" min="1" max="1"/>
+    <col width="24" customWidth="1" style="23" min="2" max="2"/>
+    <col width="24" customWidth="1" style="23" min="3" max="3"/>
+    <col width="36" customWidth="1" style="23" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1" s="23">
+      <c r="A1" s="48" t="inlineStr">
+        <is>
+          <t>绿城中国策划活动类效果评估表</t>
+        </is>
+      </c>
+      <c r="B1" s="49" t="n"/>
+      <c r="C1" s="49" t="n"/>
+      <c r="D1" s="49" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1" s="23">
+      <c r="A2" s="50" t="inlineStr">
+        <is>
+          <t>（冠名、活动赞助、活动执行等）　项目：上海绿城 · 潮鸣外滩　活动：开盘花束定制</t>
+        </is>
+      </c>
+      <c r="B2" s="51" t="n"/>
+      <c r="C2" s="51" t="n"/>
+      <c r="D2" s="51" t="n"/>
+    </row>
+    <row r="3" ht="28" customHeight="1" s="23">
+      <c r="A3" s="52" t="inlineStr">
+        <is>
+          <t>活动主题</t>
+        </is>
+      </c>
+      <c r="B3" s="53" t="inlineStr">
+        <is>
+          <t>绿城潮鳴开盘花束定制</t>
+        </is>
+      </c>
+      <c r="C3" s="32" t="n"/>
+      <c r="D3" s="32" t="n"/>
+    </row>
+    <row r="4" ht="28" customHeight="1" s="23">
+      <c r="A4" s="52" t="inlineStr">
+        <is>
+          <t>活动举办时间</t>
+        </is>
+      </c>
+      <c r="B4" s="54" t="inlineStr">
+        <is>
+          <t>2026年3月　　潮鳴东方项目示范区开放：3月26日</t>
+        </is>
+      </c>
+      <c r="C4" s="32" t="n"/>
+      <c r="D4" s="32" t="n"/>
+    </row>
+    <row r="5" ht="28" customHeight="1" s="23">
+      <c r="A5" s="52" t="inlineStr">
+        <is>
+          <t>活动
+现场氛围</t>
+        </is>
+      </c>
+      <c r="B5" s="34" t="inlineStr">
+        <is>
+          <t>① 案场大厅陈列：绿城中国标识 +「潮鸣」背景，花束装箱陈列</t>
+        </is>
+      </c>
+      <c r="C5" s="55" t="n"/>
+      <c r="D5" s="34" t="inlineStr">
+        <is>
+          <t>② 开盘现场氛围：礼仪接待、花束阵列与拍摄设备</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="78" customHeight="1" s="23">
+      <c r="A6" s="32" t="n"/>
+      <c r="B6" s="32" t="n"/>
+      <c r="C6" s="56" t="n"/>
+      <c r="D6" s="32" t="n"/>
+    </row>
+    <row r="7" ht="78" customHeight="1" s="23">
+      <c r="A7" s="32" t="n"/>
+      <c r="B7" s="57" t="n"/>
+      <c r="C7" s="58" t="n"/>
+      <c r="D7" s="59" t="n"/>
+    </row>
+    <row r="8" ht="78" customHeight="1" s="23">
+      <c r="A8" s="32" t="n"/>
+      <c r="B8" s="60" t="n"/>
+      <c r="C8" s="61" t="n"/>
+      <c r="D8" s="62" t="n"/>
+    </row>
+    <row r="9" ht="28" customHeight="1" s="23">
+      <c r="A9" s="32" t="n"/>
+      <c r="B9" s="34" t="inlineStr">
+        <is>
+          <t>③ 花束送达：厢式货车卸货（纸箱内红粉花束）</t>
+        </is>
+      </c>
+      <c r="C9" s="55" t="n"/>
+      <c r="D9" s="34" t="inlineStr">
+        <is>
+          <t>④ 花束清点转运：纸箱「鲜切花 轻拿轻放」，送达车辆 沪A·ZR373</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="78" customHeight="1" s="23">
+      <c r="A10" s="32" t="n"/>
+      <c r="B10" s="32" t="n"/>
+      <c r="C10" s="56" t="n"/>
+      <c r="D10" s="32" t="n"/>
+    </row>
+    <row r="11" ht="78" customHeight="1" s="23">
+      <c r="A11" s="32" t="n"/>
+      <c r="B11" s="57" t="n"/>
+      <c r="C11" s="58" t="n"/>
+      <c r="D11" s="59" t="n"/>
+    </row>
+    <row r="12" ht="78" customHeight="1" s="23">
+      <c r="A12" s="32" t="n"/>
+      <c r="B12" s="60" t="n"/>
+      <c r="C12" s="61" t="n"/>
+      <c r="D12" s="62" t="n"/>
+    </row>
+    <row r="13" ht="24" customHeight="1" s="23">
+      <c r="A13" s="52" t="inlineStr">
+        <is>
+          <t>策划负责人填写</t>
+        </is>
+      </c>
+      <c r="B13" s="63" t="inlineStr">
+        <is>
+          <t>总体活动评价：</t>
+        </is>
+      </c>
+      <c r="C13" s="64" t="n"/>
+      <c r="D13" s="55" t="n"/>
+    </row>
+    <row r="14" ht="36" customHeight="1" s="23">
+      <c r="A14" s="32" t="n"/>
+      <c r="B14" s="65" t="inlineStr">
+        <is>
+          <t>本次活动为潮鳴东方项目示范区开放（3月26日）。为潮鸣外滩开盘活动提供了45束鲜花。按照约定进行本次活动的整体策划与执行，活动取得圆满成功。</t>
+        </is>
+      </c>
+      <c r="C14" s="66" t="n"/>
+      <c r="D14" s="56" t="n"/>
+    </row>
+    <row r="15" ht="36" customHeight="1" s="23">
+      <c r="A15" s="32" t="n"/>
+      <c r="B15" s="60" t="n"/>
+      <c r="C15" s="67" t="n"/>
+      <c r="D15" s="61" t="n"/>
+    </row>
+    <row r="16" ht="32" customHeight="1" s="23">
+      <c r="A16" s="32" t="n"/>
+      <c r="B16" s="68" t="inlineStr">
+        <is>
+          <t>策划负责人签名：____________________　　日期：____________________　　（评估表原件此栏为空，请补签）</t>
+        </is>
+      </c>
+      <c r="C16" s="64" t="n"/>
+      <c r="D16" s="55" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" s="23">
+      <c r="A17" s="52" t="inlineStr">
+        <is>
+          <t>营销负责人填写</t>
+        </is>
+      </c>
+      <c r="B17" s="63" t="inlineStr">
+        <is>
+          <t>对活动【总体效果】评估（文字说明）：</t>
+        </is>
+      </c>
+      <c r="C17" s="64" t="n"/>
+      <c r="D17" s="55" t="n"/>
+    </row>
+    <row r="18" ht="42" customHeight="1" s="23">
+      <c r="A18" s="32" t="n"/>
+      <c r="B18" s="69" t="inlineStr">
+        <is>
+          <t>现场氛围良好，45 束鲜花按时送达并完成案场陈列，绿城中国 /「潮鸣」品牌露出清晰，与策划评价「圆满成功」一致。效果良好，符合要求。</t>
+        </is>
+      </c>
+      <c r="C18" s="64" t="n"/>
+      <c r="D18" s="55" t="n"/>
+    </row>
+    <row r="19" ht="28" customHeight="1" s="23">
+      <c r="A19" s="32" t="n"/>
+      <c r="B19" s="70" t="inlineStr">
+        <is>
+          <t>非常好（☐）　　良好（☑）　　一般（☐）　　较差（☐）</t>
+        </is>
+      </c>
+      <c r="C19" s="64" t="n"/>
+      <c r="D19" s="55" t="n"/>
+    </row>
+    <row r="20" ht="42" customHeight="1" s="23">
+      <c r="A20" s="32" t="n"/>
+      <c r="B20" s="71" t="inlineStr">
+        <is>
+          <t>勾选说明：评估表 Word 原件四档勾选栏均为空白；本表按《基础营销验收单》模板默认口径「效果良好，符合要求」勾选「良好」，不拔高为「非常好」。请营销负责人复核。</t>
+        </is>
+      </c>
+      <c r="C20" s="64" t="n"/>
+      <c r="D20" s="55" t="n"/>
+    </row>
+    <row r="21" ht="32" customHeight="1" s="23">
+      <c r="A21" s="32" t="n"/>
+      <c r="B21" s="68" t="inlineStr">
+        <is>
+          <t>营销负责人签名：____________________　　日期：____________________　　（评估表原件此栏为空，请补签）</t>
+        </is>
+      </c>
+      <c r="C21" s="64" t="n"/>
+      <c r="D21" s="55" t="n"/>
+    </row>
+    <row r="22" ht="36" customHeight="1" s="23">
+      <c r="A22" s="72" t="inlineStr">
+        <is>
+          <t>详见附件：绿城中国策划活动类效果评估表-开盘花束（Word 原件已随本工作簿打包）；费用清单由经办人签字后另附。合作金额评估表未列明，以双方约定为准。</t>
+        </is>
+      </c>
+      <c r="B22" s="32" t="n"/>
+      <c r="C22" s="32" t="n"/>
+      <c r="D22" s="32" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="D10:D12"/>
+    <mergeCell ref="B10:C12"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B14:D15"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B6:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="A5:A12"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FFF8E1"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" style="23" min="1" max="1"/>
+    <col width="16" customWidth="1" style="23" min="2" max="2"/>
+    <col width="36" customWidth="1" style="23" min="3" max="3"/>
+    <col width="28" customWidth="1" style="23" min="4" max="4"/>
+    <col width="12" customWidth="1" style="23" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" s="23">
+      <c r="A1" s="48" t="inlineStr">
+        <is>
+          <t>绿城潮鳴开盘花束定制 · 交付核验清单</t>
+        </is>
+      </c>
+      <c r="B1" s="49" t="n"/>
+      <c r="C1" s="49" t="n"/>
+      <c r="D1" s="49" t="n"/>
+      <c r="E1" s="49" t="n"/>
+    </row>
+    <row r="2" ht="28" customHeight="1" s="23">
+      <c r="A2" s="73" t="inlineStr">
+        <is>
+          <t>项目：绿城中国 · 绿城·潮鸣外滩（潮鳴东方项目示范区）　时间：2026年3月（示范区开放 3月26日）　交付：45 束鲜花　依据：绿城中国策划活动类效果评估表-开盘花束</t>
+        </is>
+      </c>
+      <c r="B2" s="51" t="n"/>
+      <c r="C2" s="51" t="n"/>
+      <c r="D2" s="51" t="n"/>
+      <c r="E2" s="51" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1" s="23">
+      <c r="A3" s="74" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B3" s="74" t="inlineStr">
+        <is>
+          <t>验收项</t>
+        </is>
+      </c>
+      <c r="C3" s="74" t="inlineStr">
+        <is>
+          <t>约定 / 载明内容</t>
+        </is>
+      </c>
+      <c r="D3" s="74" t="inlineStr">
+        <is>
+          <t>现场核验</t>
+        </is>
+      </c>
+      <c r="E3" s="74" t="inlineStr">
+        <is>
+          <t>结论</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1" s="23">
+      <c r="A4" s="75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="75" t="inlineStr">
+        <is>
+          <t>活动主题</t>
+        </is>
+      </c>
+      <c r="C4" s="72" t="inlineStr">
+        <is>
+          <t>绿城潮鳴开盘花束定制</t>
+        </is>
+      </c>
+      <c r="D4" s="72" t="inlineStr">
+        <is>
+          <t>与评估表原文一致</t>
+        </is>
+      </c>
+      <c r="E4" s="76" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1" s="23">
+      <c r="A5" s="75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" s="75" t="inlineStr">
+        <is>
+          <t>举办时间</t>
+        </is>
+      </c>
+      <c r="C5" s="72" t="inlineStr">
+        <is>
+          <t>2026年3月</t>
+        </is>
+      </c>
+      <c r="D5" s="72" t="inlineStr">
+        <is>
+          <t>示范区开放日 3月26日已载明</t>
+        </is>
+      </c>
+      <c r="E5" s="76" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1" s="23">
+      <c r="A6" s="75" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="75" t="inlineStr">
+        <is>
+          <t>项目 / 案场</t>
+        </is>
+      </c>
+      <c r="C6" s="72" t="inlineStr">
+        <is>
+          <t>潮鸣外滩开盘；潮鳴东方项目示范区</t>
+        </is>
+      </c>
+      <c r="D6" s="72" t="inlineStr">
+        <is>
+          <t>案场大厅绿城中国 +「潮鸣」背景（图①②）</t>
+        </is>
+      </c>
+      <c r="E6" s="76" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1" s="23">
+      <c r="A7" s="75" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B7" s="75" t="inlineStr">
+        <is>
+          <t>交付数量</t>
+        </is>
+      </c>
+      <c r="C7" s="72" t="inlineStr">
+        <is>
+          <t>45 束鲜花</t>
+        </is>
+      </c>
+      <c r="D7" s="72" t="inlineStr">
+        <is>
+          <t>评估表载明 45 束；现场照片见装箱/卸货陈列</t>
+        </is>
+      </c>
+      <c r="E7" s="76" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1" s="23">
+      <c r="A8" s="75" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B8" s="75" t="inlineStr">
+        <is>
+          <t>送达方式</t>
+        </is>
+      </c>
+      <c r="C8" s="72" t="inlineStr">
+        <is>
+          <t>开盘现场送达、卸货、清点</t>
+        </is>
+      </c>
+      <c r="D8" s="72" t="inlineStr">
+        <is>
+          <t>厢式货车卸货（图③）</t>
+        </is>
+      </c>
+      <c r="E8" s="76" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1" s="23">
+      <c r="A9" s="75" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B9" s="75" t="inlineStr">
+        <is>
+          <t>包装要求</t>
+        </is>
+      </c>
+      <c r="C9" s="72" t="inlineStr">
+        <is>
+          <t>鲜切花轻拿轻放</t>
+        </is>
+      </c>
+      <c r="D9" s="72" t="inlineStr">
+        <is>
+          <t>纸箱印刷「鲜切花 轻拿轻放」（图④）</t>
+        </is>
+      </c>
+      <c r="E9" s="76" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1" s="23">
+      <c r="A10" s="75" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B10" s="75" t="inlineStr">
+        <is>
+          <t>送达车辆</t>
+        </is>
+      </c>
+      <c r="C10" s="72" t="inlineStr">
+        <is>
+          <t>现场转运车辆</t>
+        </is>
+      </c>
+      <c r="D10" s="72" t="inlineStr">
+        <is>
+          <t>车牌 沪A·ZR373（图④）</t>
+        </is>
+      </c>
+      <c r="E10" s="76" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1" s="23">
+      <c r="A11" s="75" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B11" s="75" t="inlineStr">
+        <is>
+          <t>现场陈列</t>
+        </is>
+      </c>
+      <c r="C11" s="72" t="inlineStr">
+        <is>
+          <t>案场大厅花束阵列 / 礼仪接待氛围</t>
+        </is>
+      </c>
+      <c r="D11" s="72" t="inlineStr">
+        <is>
+          <t>图①②可核验陈列与拍摄现场</t>
+        </is>
+      </c>
+      <c r="E11" s="76" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1" s="23">
+      <c r="A12" s="75" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B12" s="75" t="inlineStr">
+        <is>
+          <t>品牌露出</t>
+        </is>
+      </c>
+      <c r="C12" s="72" t="inlineStr">
+        <is>
+          <t>绿城中国标识、「潮鸣」背景字</t>
+        </is>
+      </c>
+      <c r="D12" s="72" t="inlineStr">
+        <is>
+          <t>图①②案场背景清晰可辨</t>
+        </is>
+      </c>
+      <c r="E12" s="76" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1" s="23">
+      <c r="A13" s="75" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" s="75" t="inlineStr">
+        <is>
+          <t>策划评价</t>
+        </is>
+      </c>
+      <c r="C13" s="72" t="inlineStr">
+        <is>
+          <t>按约定完成整体策划与执行，圆满成功</t>
+        </is>
+      </c>
+      <c r="D13" s="72" t="inlineStr">
+        <is>
+          <t>评估表策划栏原文已转录至「效果评估表」页</t>
+        </is>
+      </c>
+      <c r="E13" s="76" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1" s="23">
+      <c r="A14" s="75" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B14" s="75" t="inlineStr">
+        <is>
+          <t>营销评估</t>
+        </is>
+      </c>
+      <c r="C14" s="72" t="inlineStr">
+        <is>
+          <t>非常好 / 良好 / 一般 / 较差</t>
+        </is>
+      </c>
+      <c r="D14" s="72" t="inlineStr">
+        <is>
+          <t>原件勾选栏空白；本表按模板「效果良好，符合要求」预勾「良好」</t>
+        </is>
+      </c>
+      <c r="E14" s="77" t="inlineStr">
+        <is>
+          <t>待补签</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1" s="23">
+      <c r="A15" s="75" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B15" s="75" t="inlineStr">
+        <is>
+          <t>合作金额</t>
+        </is>
+      </c>
+      <c r="C15" s="72" t="inlineStr">
+        <is>
+          <t>评估表未列明单价或总价</t>
+        </is>
+      </c>
+      <c r="D15" s="72" t="inlineStr">
+        <is>
+          <t>本表合作金额栏注明「按双方约定」，不编造数字；费用清单另附</t>
+        </is>
+      </c>
+      <c r="E15" s="77" t="inlineStr">
+        <is>
+          <t>待清单</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1" s="23">
+      <c r="A16" s="75" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B16" s="75" t="inlineStr">
+        <is>
+          <t>负责人签字</t>
+        </is>
+      </c>
+      <c r="C16" s="72" t="inlineStr">
+        <is>
+          <t>策划负责人、营销负责人签名</t>
+        </is>
+      </c>
+      <c r="D16" s="72" t="inlineStr">
+        <is>
+          <t>评估表原件签字栏为空，验收单已留签字行</t>
+        </is>
+      </c>
+      <c r="E16" s="77" t="inlineStr">
+        <is>
+          <t>待补签</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1" s="23">
+      <c r="A17" s="78" t="inlineStr">
+        <is>
+          <t>验收结论：开盘花束按评估表约定完成 45 束鲜花的送达、陈列与现场氛围布置，策划评价为圆满成功；营销评估预勾「良好」，待绿城营销负责人复核签字。金额、费用清单不以本表推定。本清单不与 2026-05-22 峰会晚宴冠名验收混用。</t>
+        </is>
+      </c>
+      <c r="B17" s="79" t="n"/>
+      <c r="C17" s="79" t="n"/>
+      <c r="D17" s="79" t="n"/>
+      <c r="E17" s="79" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A17:E17"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001F6B4A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1758,24 +2893,30 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" s="23">
-      <c r="A1" s="43" t="inlineStr">
-        <is>
-          <t>绿城潮鳴开盘花束定制｜活动现场氛围（评估表附图）</t>
-        </is>
-      </c>
+      <c r="A1" s="80" t="inlineStr">
+        <is>
+          <t>绿城潮鳴开盘花束定制｜活动现场氛围（评估表附图大图）</t>
+        </is>
+      </c>
+      <c r="B1" s="49" t="n"/>
+      <c r="C1" s="49" t="n"/>
+      <c r="D1" s="49" t="n"/>
     </row>
     <row r="2" ht="42" customHeight="1" s="23">
-      <c r="A2" s="44" t="inlineStr">
+      <c r="A2" s="81" t="inlineStr">
         <is>
           <t>活动主题：绿城潮鳴开盘花束定制　　举办时间：2026年3月（示范区开放 3月26日）　　交付：为潮鸣外滩开盘活动提供 45 束鲜花。按约定完成整体策划与执行，活动取得圆满成功。</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="170" customHeight="1" s="23"/>
-    <row r="5" ht="36" customHeight="1" s="23">
+      <c r="B2" s="51" t="n"/>
+      <c r="C2" s="51" t="n"/>
+      <c r="D2" s="51" t="n"/>
+    </row>
+    <row r="4" ht="188" customHeight="1" s="23"/>
+    <row r="5" ht="40" customHeight="1" s="23">
       <c r="A5" s="45" t="inlineStr">
         <is>
-          <t>1. 案场大厅：绿城中国标识 +「潮鸣」背景，花束装箱陈列</t>
+          <t>1. 案场大厅陈列：绿城中国标识 +「潮鸣」背景，花束装箱陈列</t>
         </is>
       </c>
       <c r="C5" s="45" t="inlineStr">
@@ -1784,8 +2925,8 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="170" customHeight="1" s="23"/>
-    <row r="7" ht="36" customHeight="1" s="23">
+    <row r="6" ht="188" customHeight="1" s="23"/>
+    <row r="7" ht="40" customHeight="1" s="23">
       <c r="A7" s="45" t="inlineStr">
         <is>
           <t>3. 花束送达：厢式货车卸货（纸箱内红粉花束）</t>
@@ -1793,23 +2934,29 @@
       </c>
       <c r="C7" s="45" t="inlineStr">
         <is>
-          <t>4. 花束清点转运：鲜切花轻拿轻放，沪A·ZR373 送达现场</t>
+          <t>4. 花束清点转运：纸箱「鲜切花 轻拿轻放」，送达车辆 沪A·ZR373</t>
         </is>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1" s="23">
-      <c r="A8" s="44" t="inlineStr">
+      <c r="A8" s="82" t="inlineStr">
         <is>
           <t>策划负责人填写｜总体活动评价：本次活动为潮鳴东方项目示范区开放（3月26日）。为潮鸣外滩开盘活动提供了 45 束鲜花。按照约定进行本次活动的整体策划与执行，活动取得圆满成功。</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="28" customHeight="1" s="23">
-      <c r="A9" s="46" t="inlineStr">
-        <is>
-          <t>营销负责人填写｜总体效果评估：非常好（  ）  良好（  ）  一般（  ）  较差（  ）　　营销负责人签名：__________</t>
-        </is>
-      </c>
+      <c r="B8" s="79" t="n"/>
+      <c r="C8" s="79" t="n"/>
+      <c r="D8" s="79" t="n"/>
+    </row>
+    <row r="9" ht="32" customHeight="1" s="23">
+      <c r="A9" s="83" t="inlineStr">
+        <is>
+          <t>营销负责人填写｜总体效果评估：非常好（☐）  良好（☑）  一般（☐）  较差（☐）　　营销负责人签名：__________　　日期：__________</t>
+        </is>
+      </c>
+      <c r="B9" s="84" t="n"/>
+      <c r="C9" s="84" t="n"/>
+      <c r="D9" s="84" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -1822,8 +2969,8 @@
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>